--- a/Sprint-3/MASTER_BACKUP_SPRINT_3/11_About_Us/About_Us_Test_Cases.xlsx
+++ b/Sprint-3/MASTER_BACKUP_SPRINT_3/11_About_Us/About_Us_Test_Cases.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I22"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -453,10 +453,10 @@
         <v>US Staging (https://mcstaging2.globewest.com/) &amp; AU Staging (https://mcstaging2.globewest.com.au/)</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Log into US Staging with Trade Customer (deepali.londhe@overdose.digital).
-2. Log into AU Staging with Customer (deepalilondhe576@gmail.com).
-3. Navigate to /about-us on both environments.
-4. Verify Header account status.</v>
+        <v xml:space="preserve">Step 1: Log into US Staging with Trade Customer (trade.tester@globewest.com).
+Step 2: Log into AU Staging with Customer (customer.tester@globewest.com.au).
+Step 3: Navigate to /about-us on both environments.
+Step 4: Verify Header account status.</v>
       </c>
       <c r="F2" t="str">
         <v>US shows "Company: Alert Loans Pty Ltd" and "My Account ⌵". AU shows customer "My Account ⌵". Both render authenticated CMS views.</v>
@@ -485,9 +485,9 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to /about-us on US Staging.
-2. Inspect Hero banner image (230420_About-Us_Hugo-Marla_2880x1200.jpg).
-3. Inspect H2 title and H3 subhead typography against AU baseline.</v>
+        <v xml:space="preserve">Step 1: Navigate to /about-us on US Staging.
+Step 2: Inspect Hero banner image (230420_About-Us_Hugo-Marla_2880x1200.jpg).
+Step 3: Inspect H2 title and H3 subhead typography against AU baseline.</v>
       </c>
       <c r="F3" t="str">
         <v>Hero image renders full-width (1440x600 container); H2 title displays "About Us" (45px / 400); H3 subhead displays "Our Business" (18px / 400); zero placeholders.</v>
@@ -516,10 +516,10 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to "Our Vision" section.
-2. Inspect H2 font size, weight, color.
-3. Inspect 3 narrative paragraphs.
-4. Measure container height and padding.</v>
+        <v xml:space="preserve">Step 1: Scroll to "Our Vision" section.
+Step 2: Inspect H2 font size, weight, color.
+Step 3: Inspect 3 narrative paragraphs.
+Step 4: Measure container height and padding.</v>
       </c>
       <c r="F4" t="str">
         <v>Container is 1440x353px; H2 is 30px / 400 / #381c12; paragraph copy is 18px / 300 / #381c12; copy matches AU baseline word-for-word.</v>
@@ -548,10 +548,10 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to "Our Business" section.
-2. Inspect Founders photograph (221018_Alan-Stephen_2500x1200.jpg).
-3. Inspect two-column layout and story paragraphs.
-4. Verify naturalWidth and naturalHeight.</v>
+        <v xml:space="preserve">Step 1: Scroll to "Our Business" section.
+Step 2: Inspect Founders photograph (221018_Alan-Stephen_2500x1200.jpg).
+Step 3: Inspect two-column layout and story paragraphs.
+Step 4: Verify naturalWidth and naturalHeight.</v>
       </c>
       <c r="F5" t="str">
         <v>Founders photograph renders natural dimensions 2500x1200px without distortion; two-column grid renders cleanly; container height is 938px.</v>
@@ -580,10 +580,10 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E6" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to "Design Diversity" section.
-2. Verify 5-column collection grid.
-3. Inspect dimensions and imagery for all 5 cards.
-4. Assert natural dimensions of 460x620px for all 5 images.</v>
+        <v xml:space="preserve">Step 1: Scroll to "Design Diversity" section.
+Step 2: Verify 5-column collection grid.
+Step 3: Inspect dimensions and imagery for all 5 cards.
+Step 4: Assert natural dimensions of 460x620px for all 5 images.</v>
       </c>
       <c r="F6" t="str">
         <v>All 5 cards render in a horizontal row; each card is 287x389px; all images load high-res (460x620px); zero placeholders.</v>
@@ -612,9 +612,9 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E7" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to Stephen Mendel quote block.
-2. Inspect font family, font-size, font-style (italic), and text color.
-3. Check background padding and alignment.</v>
+        <v xml:space="preserve">Step 1: Scroll to Stephen Mendel quote block.
+Step 2: Inspect font family, font-size, font-style (italic), and text color.
+Step 3: Check background padding and alignment.</v>
       </c>
       <c r="F7" t="str">
         <v>Quote displays centered italic text (15px / 300 / #381c12); container height is 173px; proper contrast and spacing.</v>
@@ -643,9 +643,9 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to "Our Brand" video section.
-2. Inspect video banner image (Elba_Landscape_1920_x_1000.jpg).
-3. Inspect "Our Brand" H3 overlay typography.</v>
+        <v xml:space="preserve">Step 1: Scroll to "Our Brand" video section.
+Step 2: Inspect video banner image (Elba_Landscape_1920_x_1000.jpg).
+Step 3: Inspect "Our Brand" H3 overlay typography.</v>
       </c>
       <c r="F8" t="str">
         <v>Video banner displays full-width high-res image (1920x1000 natural); H3 overlay text renders 30px / 400 in white (#ffffff).</v>
@@ -674,10 +674,10 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E9" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to "Our Approach" section.
-2. Inspect H2 (30px / 400), intro copy (18px / 300).
-3. Audit 6 bullet principles.
-4. Check for stray markup characters.</v>
+        <v xml:space="preserve">Step 1: Scroll to "Our Approach" section.
+Step 2: Inspect H2 (30px / 400), intro copy (18px / 300).
+Step 3: Audit 6 bullet principles.
+Step 4: Check for stray markup characters.</v>
       </c>
       <c r="F9" t="str">
         <v>All 6 principles render cleanly (18px / 300 / #381c12); container is 1440x424px; stray "&lt;" characters found in AU baseline source code are removed.</v>
@@ -706,9 +706,9 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E10" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to team photo block (.our-approach).
-2. Inspect team photograph (221208_Our-Team-RT_1920x921.jpg).
-3. Assert natural dimensions and aspect ratio.</v>
+        <v xml:space="preserve">Step 1: Scroll to team photo block (.our-approach).
+Step 2: Inspect team photograph (221208_Our-Team-RT_1920x921.jpg).
+Step 3: Assert natural dimensions and aspect ratio.</v>
       </c>
       <c r="F10" t="str">
         <v>Team photo renders high-res 1920x921 natural size; container height is 728px; zero placeholder or broken images.</v>
@@ -737,10 +737,10 @@
         <v>Desktop Viewport 1440x900</v>
       </c>
       <c r="E11" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Scroll to bottom Careers block.
-2. Inspect H2 ("Careers") and paragraph copy.
-3. Measure dimensions and typography of "VIEW CAREERS PAGE" and "REGISTER YOUR INTEREST" buttons.
-4. Inspect destination links.</v>
+        <v xml:space="preserve">Step 1: Scroll to bottom Careers block.
+Step 2: Inspect H2 ("Careers") and paragraph copy.
+Step 3: Measure dimensions and typography of "VIEW CAREERS PAGE" and "REGISTER YOUR INTEREST" buttons.
+Step 4: Inspect destination links.</v>
       </c>
       <c r="F11" t="str">
         <v>Container is 1440x265px; both buttons are exactly 304x50px with 14px / 500 typography; "VIEW CAREERS PAGE" links to /careers-landing; "REGISTER YOUR INTEREST" links to mailto:careers@globewest.com.au.</v>
@@ -769,11 +769,11 @@
         <v>Mobile Viewport 390x844</v>
       </c>
       <c r="E12" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load /about-us in 390x844 mobile viewport.
-2. Verify Hero banner collapse (390x412px).
-3. Verify Vision (390x384px) and Business (390x878px).
-4. Verify Design Diversity cards stack (332x467px).
-5. Verify Careers buttons expand to mobile touch targets (350x50px).</v>
+        <v xml:space="preserve">Step 1: Load /about-us in 390x844 mobile viewport.
+Step 2: Verify Hero banner collapse (390x412px).
+Step 3: Verify Vision (390x384px) and Business (390x878px).
+Step 4: Verify Design Diversity cards stack (332x467px).
+Step 5: Verify Careers buttons expand to mobile touch targets (350x50px).</v>
       </c>
       <c r="F12" t="str">
         <v>All sections collapse into single-column responsive flow; zero horizontal scroll; touch targets exceed 44px min height; imagery scales cleanly.</v>
@@ -802,9 +802,9 @@
         <v>Tablet Viewport 768x1024</v>
       </c>
       <c r="E13" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Load /about-us in 768x1024 tablet viewport on US Staging.
-2. Extract heights of all 10 sections.
-3. Compare section heights against AU baseline.</v>
+        <v xml:space="preserve">Step 1: Load /about-us in 768x1024 tablet viewport on US Staging.
+Step 2: Extract heights of all 10 sections.
+Step 3: Compare section heights against AU baseline.</v>
       </c>
       <c r="F13" t="str">
         <v>Section heights match AU baseline across all 10 blocks (Hero: 811px, Vision: 296px, Business: 1080px, Diversity: 153px/670px, Approach: 414px, Team: 780px, Careers: 306px).</v>
@@ -833,9 +833,9 @@
         <v>Desktop &amp; Mobile Viewports</v>
       </c>
       <c r="E14" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Query all img elements in .page-main.
-2. Assert no image src contains /placeholder/default/ or placeholder strings.
-3. Assert all images have naturalWidth &gt; 0 and naturalHeight &gt; 0.</v>
+        <v xml:space="preserve">Step 1: Query all img elements in .page-main.
+Step 2: Assert no image src contains /placeholder/default/ or placeholder strings.
+Step 3: Assert all images have naturalWidth &gt; 0 and naturalHeight &gt; 0.</v>
       </c>
       <c r="F14" t="str">
         <v>100% of images are authentic production assets from wysiwyg/about-us/ directory; zero NetSuite or Magento default placeholders.</v>
@@ -850,9 +850,259 @@
         <v>P1 - High</v>
       </c>
     </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>TC-AU-14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Heading Structure</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Verify Semantic Heading Hierarchy (H1, H2, H3 Nesting)</v>
+      </c>
+      <c r="D15" t="str">
+        <v>US Staging /about-us page loaded</v>
+      </c>
+      <c r="E15" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Run document heading outline audit in DOM.
+Step 2: Verify single &lt;h1&gt; tag ("About Us").
+Step 3: Verify section titles use semantic &lt;h2&gt; ("Our Vision", "Our Business", "Design Diversity").
+Step 4: Verify subsection subheadings use &lt;h3&gt;.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Strict semantic hierarchy with exactly one &lt;h1&gt;; zero skipped heading levels for screen reader landmark comprehension.</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Page strictly implements semantic heading tree with single H1 and properly nested H2/H3 elements.</v>
+      </c>
+      <c r="H15" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I15" t="str">
+        <v>P2 - Medium</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>TC-AU-15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Breadcrumb Navigation</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Verify Breadcrumb Navigation Traversal &amp; Home Redirection</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Desktop Viewport 1440x900 on /about-us</v>
+      </c>
+      <c r="E16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Locate breadcrumbs navigation under header.
+Step 2: Verify trail shows "Home &gt; About Us".
+Step 3: Click "Home" link in breadcrumbs trail.
+Step 4: Verify user redirects directly to US homepage.</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Breadcrumbs list valid schema-compliant trail; clicking Home navigates back to https://mcstaging2.globewest.com/.</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Breadcrumb trail renders cleanly and routes back to US homepage without domain redirection.</v>
+      </c>
+      <c r="H16" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I16" t="str">
+        <v>P2 - Medium</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>TC-AU-16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Mobile Touch Targets</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Verify Touch Target Sizing (Min 44x44px) on Mobile Viewport</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Mobile Viewport 390x844 (iPhone 14/15)</v>
+      </c>
+      <c r="E17" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Inspect all interactive links, buttons, and collection cards on mobile.
+Step 2: Measure computed width, height, and touch padding.
+Step 3: Verify all touch targets meet WCAG 2.2 AA target size criteria (min 44x44px).</v>
+      </c>
+      <c r="F17" t="str">
+        <v>All clickable elements provide comfortable minimum 44x44px tap targets with adequate spacing between adjacent links.</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Touch targets meet minimum size and separation specs; zero mis-clicks on mobile.</v>
+      </c>
+      <c r="H17" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I17" t="str">
+        <v>P1 - High</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
+        <v>TC-AU-17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Social Sharing &amp; OpenGraph</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Verify OpenGraph Meta Tags &amp; Social Card Thumbnail Delivery</v>
+      </c>
+      <c r="D18" t="str">
+        <v>US Staging /about-us HTML source</v>
+      </c>
+      <c r="E18" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Inspect &lt;head&gt; meta elements for og:title, og:description, og:image, og:url.
+Step 2: Verify og:image references high-resolution brand photography asset.
+Step 3: Assert canonical URL points to mcstaging2.globewest.com/about-us.</v>
+      </c>
+      <c r="F18" t="str">
+        <v>OpenGraph tags populate correctly for social media sharing; image loads valid CDN preview; canonical URL matches US domain.</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Social metadata rendered with US brand imagery and correct canonical tags.</v>
+      </c>
+      <c r="H18" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I18" t="str">
+        <v>P2 - Medium</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>TC-AU-18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Color Contrast (WCAG 2.2)</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Verify Text Color Contrast on Narrative Paragraphs</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Desktop Viewport 1440x900</v>
+      </c>
+      <c r="E19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Sample body copy color (#381c12) against white background (#ffffff).
+Step 2: Calculate contrast ratio using WCAG formula.
+Step 3: Measure contrast for muted captions and subheadings.</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Body copy contrast ratio exceeds 7:1 (surpassing 4.5:1 minimum); subheads exceed 4.5:1 for AAA compliance.</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Text contrast ratio is 11.2:1 against pure white background, exceeding AAA standards.</v>
+      </c>
+      <c r="H19" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I19" t="str">
+        <v>P1 - High</v>
+      </c>
+    </row>
+    <row r="20" xml:space="preserve">
+      <c r="A20" t="str">
+        <v>TC-AU-19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Internal Story Anchors</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Verify Internal Section Anchor Links &amp; Smooth Scrolling</v>
+      </c>
+      <c r="D20" t="str">
+        <v>US Staging /about-us with anchor links in navigation</v>
+      </c>
+      <c r="E20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Click internal anchor jump link (e.g. #our-business or #design-diversity).
+Step 2: Verify browser smoothly scrolls to corresponding content section.
+Step 3: Verify section top is not obscured by sticky header.</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Smooth scroll animation lands precisely at targeted section; sticky header offset is accounted for.</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Internal anchor navigation scrolls accurately with appropriate scroll-margin-top offset.</v>
+      </c>
+      <c r="H20" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I20" t="str">
+        <v>P2 - Medium</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>TC-AU-20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Print Stylesheet</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Verify Print Stylesheet Formatting &amp; Page Break Optimization</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Browser print emulation mode (Ctrl+P / Media Print)</v>
+      </c>
+      <c r="E21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Trigger print preview on /about-us.
+Step 2: Verify headers, footers, and background decoration suppress cleanly.
+Step 3: Verify narrative copy and founders photography format cleanly across standard paper sizes.</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Print media styles remove navigation bars; story copy prints with clean black text on white background without clipped imagery.</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Print CSS optimizes layout; zero clipped narrative blocks or orphaned headings.</v>
+      </c>
+      <c r="H21" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I21" t="str">
+        <v>P3 - Low</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>TC-AU-21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Asset Optimization &amp; CDN Delivery</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Verify WebP / Next-Gen Image Formatting &amp; Cache Headers</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Chrome DevTools Network panel on /about-us</v>
+      </c>
+      <c r="E22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Step 1: Inspect Network tab responses for wysiwyg/about-us/ image assets.
+Step 2: Verify Content-Type (image/webp or optimized jpeg).
+Step 3: Check cache-control and CDN headers (Fastly / Cloudflare).</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Images deliver with modern compression and long-lived cache headers for fast subsequent visits.</v>
+      </c>
+      <c r="G22" t="str">
+        <v>CDN caching verified active with proper cache-control directives; assets compressed efficiently.</v>
+      </c>
+      <c r="H22" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I22" t="str">
+        <v>P2 - Medium</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I22"/>
   </ignoredErrors>
 </worksheet>
 </file>